--- a/v3_boq_system/outputs/project2/project2_BOQ_V3.xlsx
+++ b/v3_boq_system/outputs/project2/project2_BOQ_V3.xlsx
@@ -3555,7 +3555,7 @@
       </c>
       <c r="H117" s="18" t="inlineStr">
         <is>
-          <t>Gross 92.16 m² − doors 1.877 m² [DOOR_90×1(0.920×2.04)] − windows 12.775 m² [WINDOW_LOUVRE_1100×8(1.080×1.20), WINDOW_LO</t>
+          <t>[canonical_geometry] Gross=92.16 m² (38.40 m × 2.4 m). Entrance doors: 1.877 m² [DOOR_90×1(0.920×2.040m)]. Windows: 12.7</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="H184" s="18" t="inlineStr">
         <is>
-          <t>Opening deductions (assumed-internal doors, both partition faces): 16.320 m² [DOOR_82×4×2f(0.820×2.04), DOOR_72×1×2f(0.7</t>
+          <t>[canonical_geometry] Partition door deductions (both faces): 16.320 m² [DOOR_82×4×2f(0.820×2.040), DOOR_72×1×2f(0.720×2.</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="H186" s="10" t="inlineStr">
         <is>
-          <t>Opening deductions: doors=1.877 m² [DOOR_90×1(0.920×2.04)]; windows=12.775 m² [WINDOW_LOUVRE_1100×8(1.080×0.75), WINDOW_</t>
+          <t>[canonical_geometry] Opening deductions: doors=1.877 m² [DOOR_90×1(0.920×2.040)]; windows=12.775 m² [WINDOW_LOUVRE_1100×</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="H190" s="28" t="inlineStr">
         <is>
-          <t>Opening deductions (assumed-internal doors, both partition faces): 16.320 m² [DOOR_82×4×2f(0.820×2.04), DOOR_72×1×2f(0.7</t>
+          <t>[canonical_geometry] Partition door deductions (both faces): 16.320 m² [DOOR_82×4×2f(0.820×2.040), DOOR_72×1×2f(0.720×2.</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="D93" s="38" t="inlineStr">
         <is>
-          <t>calculated</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="E93" s="38" t="n"/>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="I93" s="39" t="inlineStr">
         <is>
-          <t>Gross 92.16 m² − doors 1.877 m² [DOOR_90×1(0.920×2.04)] − windows 12.775 m² [WINDOW_LOUVRE_1100×8(1.080×1.20), WINDOW_LOUVRE_800×2(0.799×0.62), WINDOW_LOUVRE_1800×1(1.847×0.75)] (louvre h=0.75 m from config default) = net 77.51 m². Partition doors (&lt;0.85 m wide) excluded — not in external cladding face.</t>
+          <t>[canonical_geometry] Gross=92.16 m² (38.40 m × 2.4 m). Entrance doors: 1.877 m² [DOOR_90×1(0.920×2.040m)]. Windows: 12.775 m² [WINDOW_LOUVRE_1100×8(1.080×1.203m); WINDOW_LOUVRE_800×2(0.799×0.623m); WINDOW_LOUVRE_1800×1(1.847×0.750m [louvre_fallback])] (louvre_h_default=0.75 m). Net cladding: 77.51 m². Partition doors excluded (width &lt; 0.85 m — internal walls only).</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>dxf_geometry</t>
+          <t>canonical_geometry</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>calculated</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="E162" s="20" t="n"/>
@@ -12962,12 +12962,12 @@
       </c>
       <c r="H162" s="20" t="inlineStr">
         <is>
-          <t>dxf_geometry</t>
+          <t>canonical_geometry/wf_external</t>
         </is>
       </c>
       <c r="I162" s="21" t="inlineStr">
         <is>
-          <t>Opening deductions: doors=1.877 m² [DOOR_90×1(0.920×2.04)]; windows=12.775 m² [WINDOW_LOUVRE_1100×8(1.080×0.75), WINDOW_LOUVRE_800×2(0.799×0.75), WINDOW_LOUVRE_1800×1(1.847×0.75)] (louvre height=0.75 m from config default). Gross=92.16 m² − 14.652 m² = net=77.51 m².</t>
+          <t>[canonical_geometry] Opening deductions: doors=1.877 m² [DOOR_90×1(0.920×2.040)]; windows=12.775 m² [WINDOW_LOUVRE_1100×8(1.080×1.203), WINDOW_LOUVRE_800×2(0.799×0.623), WINDOW_LOUVRE_1800×1(1.847×0.750 [louvre_fallback])] (louvre_h=0.75 m). Gross=92.16 m² − 14.652 m² = net=77.51 m².</t>
         </is>
       </c>
     </row>
@@ -13111,7 +13111,7 @@
       </c>
       <c r="D167" s="20" t="inlineStr">
         <is>
-          <t>calculated</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="E167" s="20" t="n"/>
@@ -13123,12 +13123,12 @@
       </c>
       <c r="H167" s="20" t="inlineStr">
         <is>
-          <t>dxf_geometry</t>
+          <t>canonical_geometry/wf_internal</t>
         </is>
       </c>
       <c r="I167" s="21" t="inlineStr">
         <is>
-          <t>Opening deductions (assumed-internal doors, both partition faces): 16.320 m² [DOOR_82×4×2f(0.820×2.04), DOOR_72×1×2f(0.720×2.04)]. Gross=141.12 m² − 16.320 m² = net=124.80 m². Doors classified as internal by width &lt; 0.85 m threshold. Measured from DXF WALLS layer: 8 internal wall runs.</t>
+          <t>[canonical_geometry] Partition door deductions (both faces): 16.320 m² [DOOR_82×4×2f(0.820×2.040), DOOR_72×1×2f(0.720×2.040)]. Gross=141.12 m² − 16.320 m² = net=124.80 m². Doors classified internal by width &lt; 0.85 m threshold. Measured from DXF WALLS layer: 8 internal wall runs.</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="I169" s="21" t="inlineStr">
         <is>
-          <t>Opening deductions (assumed-internal doors, both partition faces): 16.320 m² [DOOR_82×4×2f(0.820×2.04), DOOR_72×1×2f(0.720×2.04)]. Gross=141.12 m² − 16.320 m² = net=124.80 m². Doors classified as internal by width &lt; 0.85 m threshold. Measured from DXF WALLS layer: 8 internal wall runs.</t>
+          <t>[canonical_geometry] Partition door deductions (both faces): 16.320 m² [DOOR_82×4×2f(0.820×2.040), DOOR_72×1×2f(0.720×2.040)]. Gross=141.12 m² − 16.320 m² = net=124.80 m². Doors classified internal by width &lt; 0.85 m threshold. Measured from DXF WALLS layer: 8 internal wall runs.</t>
         </is>
       </c>
     </row>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="H87" s="62" t="inlineStr">
         <is>
-          <t>calculated</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="I87" s="62" t="inlineStr">
@@ -22260,7 +22260,7 @@
       </c>
       <c r="J98" s="62" t="inlineStr">
         <is>
-          <t>dxf_geometry: 4 openings in external cladding face</t>
+          <t>canonical_geometry: 4 openings in cladding face</t>
         </is>
       </c>
       <c r="K98" s="62" t="inlineStr">
@@ -25609,7 +25609,7 @@
       </c>
       <c r="H154" s="62" t="inlineStr">
         <is>
-          <t>calculated</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="I154" s="62" t="inlineStr">
@@ -25619,7 +25619,7 @@
       </c>
       <c r="J154" s="62" t="inlineStr">
         <is>
-          <t>dxf_geometry: ext_wall_lm=38.40 m × h=2.4 m → gross=92.16 m² − openings=14.652 m² → net=77.51 m²</t>
+          <t>canonical_geometry/wf_external: gross=92.16 m² net=77.51 m² − openings=14.652 m² → net=77.51 m²</t>
         </is>
       </c>
       <c r="K154" s="62" t="inlineStr">
@@ -25909,7 +25909,7 @@
       </c>
       <c r="H159" s="62" t="inlineStr">
         <is>
-          <t>calculated</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="I159" s="62" t="inlineStr">
@@ -25919,7 +25919,7 @@
       </c>
       <c r="J159" s="62" t="inlineStr">
         <is>
-          <t>dxf_geometry: int_wall_lm=29.40 m × h=2.4 m × 2 faces = 141.12 m² − int_doors=16.320 m² → net=124.80 m²</t>
+          <t>canonical_geometry/wf_internal: gross=141.12 m² net=124.80 m² − int_doors=16.320 m² → net=124.80 m²</t>
         </is>
       </c>
       <c r="K159" s="62" t="inlineStr">
@@ -34936,7 +34936,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -34946,7 +34946,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7">
@@ -35198,10 +35198,10 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -35225,10 +35225,10 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -35431,7 +35431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -35493,7 +35493,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ceiling_area=49.00</t>
+          <t>canonical_geometry</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -35503,27 +35503,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>config_backed → space_model</t>
+          <t>canonical_geometry/wf_external</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>canonical_geometry/wf_internal</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>derived from clip count</t>
+          <t>ceiling_area=49.00</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -35533,177 +35533,177 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>derived from project_config</t>
+          <t>config_backed → space_model</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>derived from ramp run</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>derived_steel_floor</t>
+          <t>derived from clip count</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dxf_blocks</t>
+          <t>derived from project_config</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dxf_blocks+framecad_labels</t>
+          <t>derived from ramp run</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dxf_geometry</t>
+          <t>derived_steel_floor</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>enclosed_floor_area=64.80</t>
+          <t>dxf_blocks</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>export_layer</t>
+          <t>dxf_blocks+framecad_labels</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ext_walls</t>
+          <t>dxf_geometry</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>framecad_bom</t>
+          <t>enclosed_floor_area=64.80</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>framecad_dwg</t>
+          <t>export_layer</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>framecad_dwg+dxf_geometry</t>
+          <t>ext_walls</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>framecad_layout</t>
+          <t>framecad_bom</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>framecad_panel_label_ocr</t>
+          <t>framecad_dwg</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ifc_model</t>
+          <t>framecad_dwg+dxf_geometry</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>framecad_layout</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>project_config</t>
+          <t>framecad_panel_label_ocr</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>room</t>
+          <t>ifc_model</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -35713,30 +35713,60 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>room_schedule</t>
+          <t>no</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>spaces=['Toilet']</t>
+          <t>project_config</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>room</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>room_schedule</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>spaces=['Toilet']</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>total_paint_area=282.28</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B37" t="n">
         <v>1</v>
       </c>
     </row>
